--- a/1.3.Java_FSD_Optimized_100hrs reduced to Modified to 88 Hrs.xlsx
+++ b/1.3.Java_FSD_Optimized_100hrs reduced to Modified to 88 Hrs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SLP13091\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KRCT-Java Full Stack Developer\KRCT Java Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7AD411-DE73-421A-9282-6C0E5ECFA175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -567,14 +567,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -590,12 +582,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -603,8 +589,22 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -871,7 +871,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -879,185 +879,190 @@
     <col min="4" max="4" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-    </row>
-    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+    </row>
+    <row r="4" spans="1:4" ht="28" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:4" ht="27" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="4">
         <v>28</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="27" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:4" ht="27" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="4">
         <v>33</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="27" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="4">
         <v>26</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="27" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="4">
         <v>13</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
-      <c r="B9" s="11" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="6"/>
+      <c r="B9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="6">
         <f>SUM(C5:C8)</f>
         <v>100</v>
       </c>
-      <c r="D9" s="10"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="D9" s="6"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="1:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+    </row>
+    <row r="12" spans="1:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-    </row>
-    <row r="13" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+    </row>
+    <row r="13" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-    </row>
-    <row r="14" spans="1:4" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+    </row>
+    <row r="14" spans="1:4" ht="62.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-    </row>
-    <row r="15" spans="1:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+    </row>
+    <row r="15" spans="1:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-    </row>
-    <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+    </row>
+    <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-    </row>
-    <row r="17" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+    </row>
+    <row r="17" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-    </row>
-    <row r="18" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+    </row>
+    <row r="18" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-    </row>
-    <row r="19" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+    </row>
+    <row r="19" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-    </row>
-    <row r="20" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+    </row>
+    <row r="20" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A14:D14"/>
@@ -1065,11 +1070,6 @@
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1079,7 +1079,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -1088,227 +1088,233 @@
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-    </row>
-    <row r="3" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+    </row>
+    <row r="3" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
+    <row r="5" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+    <row r="6" spans="1:5" ht="37.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="16">
         <v>2</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="16">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="14" t="s">
+    <row r="7" spans="1:5" ht="27" x14ac:dyDescent="0.35">
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5" ht="25.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="E7" s="16"/>
+    </row>
+    <row r="8" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="16">
         <v>3</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="16">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="14" t="s">
+    <row r="9" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="A10" s="12">
+      <c r="E9" s="16"/>
+    </row>
+    <row r="10" spans="1:5" ht="27" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
         <v>4</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
+    <row r="11" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
         <v>5</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="25.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+    <row r="12" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="16">
         <v>6</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="16">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="14" t="s">
+    <row r="13" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:5" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="E13" s="16"/>
+    </row>
+    <row r="14" spans="1:5" ht="37.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="16">
         <v>7</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="16">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="14" t="s">
+    <row r="15" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15" t="s">
+      <c r="E15" s="16"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="16">
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="10">
         <f>SUM(E5:E15)</f>
         <v>28</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="E6:E7"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="E14:E15"/>
@@ -1318,12 +1324,6 @@
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="E12:E13"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="E6:E7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1333,7 +1333,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -1342,193 +1342,193 @@
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-    </row>
-    <row r="3" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+    </row>
+    <row r="3" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="25.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+    <row r="5" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="16">
         <v>1</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="16">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="14" t="s">
+    <row r="6" spans="1:5" ht="27" x14ac:dyDescent="0.35">
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5" ht="54" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="14" t="s">
+      <c r="E6" s="16"/>
+    </row>
+    <row r="7" spans="1:5" ht="54" x14ac:dyDescent="0.35">
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="14" t="s">
+      <c r="E7" s="16"/>
+    </row>
+    <row r="8" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
+      <c r="E8" s="16"/>
+    </row>
+    <row r="9" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
         <v>2</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="54" x14ac:dyDescent="0.25">
-      <c r="A10" s="12">
+    <row r="10" spans="1:5" ht="54" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
         <v>3</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
+    <row r="11" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
         <v>4</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="12">
+    <row r="12" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
         <v>5</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="12">
+    <row r="13" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
         <v>6</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="16">
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="10">
         <f>SUM(E5:E13)</f>
         <v>33</v>
       </c>
@@ -1550,7 +1550,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -1559,199 +1559,199 @@
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-    </row>
-    <row r="3" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+    </row>
+    <row r="3" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="54" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
+    <row r="5" spans="1:5" ht="54" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+    <row r="6" spans="1:5" ht="37.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="16">
         <v>2</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="16">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="14" t="s">
+    <row r="7" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5" ht="25.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="E7" s="16"/>
+    </row>
+    <row r="8" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="16">
         <v>3</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="16">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="14" t="s">
+    <row r="9" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="14" t="s">
+      <c r="E9" s="16"/>
+    </row>
+    <row r="10" spans="1:5" ht="27" x14ac:dyDescent="0.35">
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="14" t="s">
+      <c r="E10" s="16"/>
+    </row>
+    <row r="11" spans="1:5" ht="27" x14ac:dyDescent="0.35">
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:5" ht="25.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="E11" s="16"/>
+    </row>
+    <row r="12" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="16">
         <v>4</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="16">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="14" t="s">
+    <row r="13" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15" t="s">
+      <c r="E13" s="16"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="16">
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="10">
         <f>SUM(E5:E13)</f>
         <v>26</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="E6:E7"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="E8:E11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="E12:E13"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="E6:E7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1761,7 +1761,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -1770,109 +1770,109 @@
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-    </row>
-    <row r="3" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+    </row>
+    <row r="3" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
+    <row r="5" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="12">
+    <row r="6" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
         <v>2</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
+    <row r="7" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
         <v>3</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="16">
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="10">
         <f>SUM(E5:E7)</f>
         <v>13</v>
       </c>

--- a/1.3.Java_FSD_Optimized_100hrs reduced to Modified to 88 Hrs.xlsx
+++ b/1.3.Java_FSD_Optimized_100hrs reduced to Modified to 88 Hrs.xlsx
@@ -596,15 +596,15 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -977,92 +977,87 @@
       <c r="D9" s="6"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
     </row>
     <row r="12" spans="1:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
     </row>
     <row r="13" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
     </row>
     <row r="14" spans="1:4" ht="62.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
     </row>
     <row r="15" spans="1:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
     </row>
     <row r="17" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
     </row>
     <row r="18" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
     </row>
     <row r="19" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
     </row>
     <row r="20" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A13:D13"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A14:D14"/>
@@ -1070,6 +1065,11 @@
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1150,10 +1150,10 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="37.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="16">
+      <c r="A6" s="14">
         <v>2</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="15" t="s">
         <v>39</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -1162,26 +1162,26 @@
       <c r="D6" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="14">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="27" x14ac:dyDescent="0.35">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
       <c r="C7" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="16"/>
+      <c r="E7" s="14"/>
     </row>
     <row r="8" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="16">
+      <c r="A8" s="14">
         <v>3</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="15" t="s">
         <v>44</v>
       </c>
       <c r="C8" s="8" t="s">
@@ -1190,20 +1190,20 @@
       <c r="D8" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="14">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
       <c r="C9" s="8" t="s">
         <v>47</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="16"/>
+      <c r="E9" s="14"/>
     </row>
     <row r="10" spans="1:5" ht="27" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
@@ -1240,10 +1240,10 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="16">
+      <c r="A12" s="14">
         <v>6</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="15" t="s">
         <v>55</v>
       </c>
       <c r="C12" s="8" t="s">
@@ -1252,26 +1252,26 @@
       <c r="D12" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="14">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
       <c r="C13" s="8" t="s">
         <v>58</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="16"/>
+      <c r="E13" s="14"/>
     </row>
     <row r="14" spans="1:5" ht="37.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="16">
+      <c r="A14" s="14">
         <v>7</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="15" t="s">
         <v>60</v>
       </c>
       <c r="C14" s="8" t="s">
@@ -1280,20 +1280,20 @@
       <c r="D14" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="14">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
       <c r="C15" s="8" t="s">
         <v>63</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="16"/>
+      <c r="E15" s="14"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="9"/>
@@ -1309,12 +1309,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="E6:E7"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="E14:E15"/>
@@ -1324,6 +1318,12 @@
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="E12:E13"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="E6:E7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1387,10 +1387,10 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="16">
+      <c r="A5" s="14">
         <v>1</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="15" t="s">
         <v>69</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -1399,42 +1399,42 @@
       <c r="D5" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="14">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="27" x14ac:dyDescent="0.35">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
       <c r="C6" s="8" t="s">
         <v>72</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="E6" s="16"/>
+      <c r="E6" s="14"/>
     </row>
     <row r="7" spans="1:5" ht="54" x14ac:dyDescent="0.35">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
       <c r="C7" s="8" t="s">
         <v>74</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="16"/>
+      <c r="E7" s="14"/>
     </row>
     <row r="8" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="16"/>
-      <c r="B8" s="16"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
       <c r="C8" s="8" t="s">
         <v>76</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="E8" s="16"/>
+      <c r="E8" s="14"/>
     </row>
     <row r="9" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
@@ -1621,10 +1621,10 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="37.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="16">
+      <c r="A6" s="14">
         <v>2</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="15" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -1633,26 +1633,26 @@
       <c r="D6" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="14">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
       <c r="C7" s="8" t="s">
         <v>102</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="E7" s="16"/>
+      <c r="E7" s="14"/>
     </row>
     <row r="8" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="16">
+      <c r="A8" s="14">
         <v>3</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="15" t="s">
         <v>104</v>
       </c>
       <c r="C8" s="8" t="s">
@@ -1661,48 +1661,48 @@
       <c r="D8" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="14">
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
       <c r="C9" s="8" t="s">
         <v>107</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="E9" s="16"/>
+      <c r="E9" s="14"/>
     </row>
     <row r="10" spans="1:5" ht="27" x14ac:dyDescent="0.35">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
       <c r="C10" s="8" t="s">
         <v>109</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="E10" s="16"/>
+      <c r="E10" s="14"/>
     </row>
     <row r="11" spans="1:5" ht="27" x14ac:dyDescent="0.35">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
       <c r="C11" s="8" t="s">
         <v>111</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="E11" s="16"/>
+      <c r="E11" s="14"/>
     </row>
     <row r="12" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="16">
+      <c r="A12" s="14">
         <v>4</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="15" t="s">
         <v>113</v>
       </c>
       <c r="C12" s="8" t="s">
@@ -1711,20 +1711,20 @@
       <c r="D12" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="14">
         <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="40.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
       <c r="C13" s="8" t="s">
         <v>116</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="E13" s="16"/>
+      <c r="E13" s="14"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="9"/>
@@ -1740,18 +1740,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="E12:E13"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="E6:E7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="E8:E11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="E12:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
